--- a/excel_exports/石滩区分区计量.xlsx
+++ b/excel_exports/石滩区分区计量.xlsx
@@ -1166,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.28318584070797" customWidth="1" style="1" min="1" max="1"/>
@@ -4458,7 +4458,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129"/>
     <row r="130">
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -4634,8 +4633,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="0" t="inlineStr">
         <is>
           <t>2026年10月</t>
         </is>
@@ -4806,6 +4806,181 @@
         <v>0</v>
       </c>
       <c r="J142" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>荔新大道</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>宁西总表（插入式）DN1200</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>如丰大道</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>新城大道医院NB</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="inlineStr">
+        <is>
+          <t>三棵竹</t>
+        </is>
+      </c>
+      <c r="G145" s="15" t="inlineStr">
+        <is>
+          <t>供水量</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>售水量</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>损耗水量</t>
+        </is>
+      </c>
+      <c r="J145" s="13" t="inlineStr">
+        <is>
+          <t>水损耗（百分比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>1区</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>2区</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>3区</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="F149" s="15" t="inlineStr">
+        <is>
+          <t>合计:</t>
+        </is>
+      </c>
+      <c r="G149" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="19" t="n">
         <v>0</v>
       </c>
     </row>
